--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>83.60991792469315</v>
+        <v>13.58661166276264</v>
       </c>
       <c r="D2" t="n">
-        <v>83.07231457625248</v>
+        <v>13.49925111864103</v>
       </c>
       <c r="E2" t="n">
-        <v>14.07448383369417</v>
+        <v>2.287103622975303</v>
       </c>
       <c r="F2" t="n">
-        <v>17.55892758583711</v>
+        <v>2.853325732698531</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.64119906319497</v>
+        <v>7.416694847769183</v>
       </c>
       <c r="D3" t="n">
-        <v>46.55402495325671</v>
+        <v>7.565029054904215</v>
       </c>
       <c r="E3" t="n">
-        <v>14.07448383369417</v>
+        <v>2.287103622975303</v>
       </c>
       <c r="F3" t="n">
-        <v>17.55892758583711</v>
+        <v>2.853325732698531</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.16711013386494</v>
+        <v>9.127155396753054</v>
       </c>
       <c r="D4" t="n">
-        <v>70.18000565683381</v>
+        <v>11.4042509192355</v>
       </c>
       <c r="E4" t="n">
-        <v>14.07448383369417</v>
+        <v>2.287103622975303</v>
       </c>
       <c r="F4" t="n">
-        <v>17.55892758583711</v>
+        <v>2.853325732698531</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.16625589438694</v>
+        <v>9.127016582837877</v>
       </c>
       <c r="D5" t="n">
-        <v>93.61492836006641</v>
+        <v>15.21242585851079</v>
       </c>
       <c r="E5" t="n">
-        <v>14.07448383369417</v>
+        <v>2.287103622975303</v>
       </c>
       <c r="F5" t="n">
-        <v>17.55892758583711</v>
+        <v>2.853325732698531</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
